--- a/data/input/退款申请.xlsx
+++ b/data/input/退款申请.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,53 +501,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORD000024</t>
+          <t>ORD000004</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>14960</v>
+        <v>3040</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>客户个人原因</t>
+          <t>与预期不符</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -570,53 +570,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORD000010</t>
+          <t>ORD000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>14960</v>
+        <v>2520</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>皮肤过敏</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORD000015</t>
+          <t>ORD000009</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -654,38 +654,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU002</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>李婷婷</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2499</v>
+        <v>4350</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>皮肤过敏</t>
+          <t>客户个人原因</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -708,53 +708,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORD000014</t>
+          <t>ORD000008</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CU005</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孙倩倩</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>瘦脸针</t>
+          <t>面部焕新套餐</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2520</v>
+        <v>10496</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>更换项目</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -777,66 +777,135 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>ORD000017</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>广州天河店</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CU003</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>王芳芳</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I001</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>水光针</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>833</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>前台</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RF000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>ORD000003</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>S001</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>北京朝阳店</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CU006</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>周晶晶</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>I001</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>水光针</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1666</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CU004</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>赵丽丽</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>瘦脸针</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10080</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>皮肤过敏</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>前台</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
